--- a/data/trans_orig/IP05A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>72560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86681</t>
+          <t>86928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>83,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>79984</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>73152</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>85868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>88,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>159976</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>149794</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>168051</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>74,36%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>83,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79984</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73124</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>85456</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>159976</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>149932</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>168205</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>74,43%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>25369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>42492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76728</t>
+          <t>76659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60803</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72660</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130522</t>
+          <t>129550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147777</t>
+          <t>147426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51089</t>
+          <t>51475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61256</t>
+          <t>61150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81149</t>
+          <t>79931</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91130</t>
+          <t>90885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135735</t>
+          <t>135299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150103</t>
+          <t>150144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151178</t>
+          <t>151265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169530</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163941</t>
+          <t>164616</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179912</t>
+          <t>180221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>319920</t>
+          <t>321452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>345050</t>
+          <t>345819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33420</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>68989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>80912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>92431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86269</t>
+          <t>86777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>103109</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>171881</t>
+          <t>171795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>191371</t>
+          <t>191742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31071</t>
+          <t>29850</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49882</t>
+          <t>48511</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58105</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68227</t>
+          <t>67895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55062</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>65614</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116953</t>
+          <t>117569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>131660</t>
+          <t>131351</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>504187</t>
+          <t>503993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>534381</t>
+          <t>534670</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547385</t>
+          <t>545944</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>579174</t>
+          <t>577892</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1061115</t>
+          <t>1059523</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107437</t>
+          <t>1103637</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112777</t>
+          <t>113632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87068</t>
+          <t>87413</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115968</t>
+          <t>117160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>177523</t>
+          <t>179606</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>221210</t>
+          <t>222459</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27303</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>46816</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70380</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>81589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>71125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81661</t>
+          <t>81553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145370</t>
+          <t>146264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160883</t>
+          <t>161224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>74020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84273</t>
+          <t>84791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82886</t>
+          <t>82147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92487</t>
+          <t>91920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>160069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174707</t>
+          <t>174311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69643</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79758</t>
+          <t>79890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>75197</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83188</t>
+          <t>83264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>147888</t>
+          <t>148427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161186</t>
+          <t>161629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176416</t>
+          <t>176256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190342</t>
+          <t>189922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184484</t>
+          <t>182878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201750</t>
+          <t>200912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365521</t>
+          <t>364637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387728</t>
+          <t>387397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>39739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60115</t>
+          <t>61047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122832</t>
+          <t>122422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>136166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118946</t>
+          <t>119565</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131253</t>
+          <t>131287</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246121</t>
+          <t>246786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263449</t>
+          <t>263929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49008</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>58463</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67985</t>
+          <t>68371</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102211</t>
+          <t>101377</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>115477</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>576582</t>
+          <t>577328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>604817</t>
+          <t>605250</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>614864</t>
+          <t>613632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>642678</t>
+          <t>642947</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1202249</t>
+          <t>1201714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1241798</t>
+          <t>1240842</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59644</t>
+          <t>59718</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>85419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62213</t>
+          <t>61363</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>88808</t>
+          <t>90565</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>127179</t>
+          <t>128581</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>165340</t>
+          <t>166168</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27347</t>
+          <t>27611</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65941</t>
+          <t>65715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>76110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80804</t>
+          <t>80796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91245</t>
+          <t>91945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151639</t>
+          <t>150553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165402</t>
+          <t>164766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>81512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>93908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>84294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97913</t>
+          <t>98125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171506</t>
+          <t>170935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189496</t>
+          <t>189277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43817</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49593</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>57910</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>56449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>67129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109558</t>
+          <t>109233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123242</t>
+          <t>123468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178346</t>
+          <t>179550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196413</t>
+          <t>196608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167512</t>
+          <t>166751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184898</t>
+          <t>184827</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351467</t>
+          <t>352501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376303</t>
+          <t>376077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37111</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30530</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107262</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120724</t>
+          <t>120831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108301</t>
+          <t>108938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123448</t>
+          <t>123510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>221174</t>
+          <t>222173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241094</t>
+          <t>241328</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26075</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28636</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47478</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51577</t>
+          <t>52129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50267</t>
+          <t>49931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60917</t>
+          <t>60499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95452</t>
+          <t>95469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110279</t>
+          <t>110338</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>549843</t>
+          <t>549758</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>581046</t>
+          <t>579155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>573279</t>
+          <t>574610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>606030</t>
+          <t>607243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1135156</t>
+          <t>1135054</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1178540</t>
+          <t>1177607</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62080</t>
+          <t>63480</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90649</t>
+          <t>90304</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79302</t>
+          <t>78138</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108428</t>
+          <t>107602</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>147641</t>
+          <t>147572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>187483</t>
+          <t>188816</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59060</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90671</t>
+          <t>90834</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120394</t>
+          <t>120353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130581</t>
+          <t>130646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>215660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229101</t>
+          <t>228551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71037</t>
+          <t>70703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>83354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84018</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92255</t>
+          <t>92426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156815</t>
+          <t>158666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173036</t>
+          <t>173552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26512</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52182</t>
+          <t>52226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61398</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99261</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110302</t>
+          <t>110511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122175</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>207145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193001</t>
+          <t>192130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207945</t>
+          <t>207658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292518</t>
+          <t>296969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408761</t>
+          <t>408976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94384</t>
+          <t>98869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136653</t>
+          <t>130768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101355</t>
+          <t>101409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111832</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>141426</t>
+          <t>141349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155224</t>
+          <t>155824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247621</t>
+          <t>247404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266115</t>
+          <t>266055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28418</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13291,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64328</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>60559</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>128332</t>
+          <t>128561</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137537</t>
+          <t>137437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>483410</t>
+          <t>490170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>606054</t>
+          <t>606064</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>675715</t>
+          <t>676920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>702711</t>
+          <t>702972</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1174040</t>
+          <t>1181609</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1299590</t>
+          <t>1299950</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161204</t>
+          <t>154179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32893</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>54837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77046</t>
+          <t>77687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>202167</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
